--- a/data/csv/sbce_config.xlsx
+++ b/data/csv/sbce_config.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszokoly\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C1FFA6-A451-4E6B-A6BE-F302955234C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4823F4AF-78F1-46A8-8700-6B3078B7E50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9974296-33B4-464A-B6B3-E66B7C96D59B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B9974296-33B4-464A-B6B3-E66B7C96D59B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Lab" sheetId="1" r:id="rId1"/>
+    <sheet name="SBCEMS" sheetId="1" r:id="rId1"/>
+    <sheet name="EMS" sheetId="2" r:id="rId2"/>
+    <sheet name="SBCE1" sheetId="3" r:id="rId3"/>
+    <sheet name="SBCE2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="137">
   <si>
     <t>datastore</t>
   </si>
@@ -302,21 +305,9 @@
     <t>sig_gw</t>
   </si>
   <si>
-    <t>SIP data interface gateway</t>
-  </si>
-  <si>
     <t>sig_ip</t>
   </si>
   <si>
-    <t>SIP data interace IP address</t>
-  </si>
-  <si>
-    <t>sig_pub_ip</t>
-  </si>
-  <si>
-    <t>SIP data interace public IP address</t>
-  </si>
-  <si>
     <t>Host type</t>
   </si>
   <si>
@@ -347,13 +338,115 @@
     <t>M1 NIC Port-group / Bridge name</t>
   </si>
   <si>
-    <t>KVM</t>
+    <t>Time Zone - Time Zone in which device is located in GMT</t>
+  </si>
+  <si>
+    <t>EMS+SBCE</t>
+  </si>
+  <si>
+    <t>SIP data interface IP address</t>
+  </si>
+  <si>
+    <t>SIP data interface default gateway</t>
+  </si>
+  <si>
+    <t>ESXI</t>
+  </si>
+  <si>
+    <t>cmb@Dm1n</t>
+  </si>
+  <si>
+    <t>192.168.11.161</t>
+  </si>
+  <si>
+    <t>root</t>
+  </si>
+  <si>
+    <t>datastore1</t>
+  </si>
+  <si>
+    <t>/home/sszokoly/Projects/sbce-automation/data/ova</t>
+  </si>
+  <si>
+    <t>sbce-vm</t>
+  </si>
+  <si>
+    <t>10.10.48.180</t>
+  </si>
+  <si>
+    <t>255.255.255.0</t>
+  </si>
+  <si>
+    <t>SBCE</t>
   </si>
   <si>
     <t>EMS</t>
   </si>
   <si>
-    <t>Time Zone - Time Zone in which device is located in GMT</t>
+    <t>10.10.48.254</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>LAB</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>GMT-7</t>
+  </si>
+  <si>
+    <t>10.10.48.250</t>
+  </si>
+  <si>
+    <t>10.10.48.92</t>
+  </si>
+  <si>
+    <t>VLAN48</t>
+  </si>
+  <si>
+    <t>Duplication</t>
+  </si>
+  <si>
+    <t>VLAN32</t>
+  </si>
+  <si>
+    <t>10.10.48.181</t>
+  </si>
+  <si>
+    <t>A1_sig</t>
+  </si>
+  <si>
+    <t>ems</t>
+  </si>
+  <si>
+    <t>10.10.48.185</t>
+  </si>
+  <si>
+    <t>sbcems</t>
+  </si>
+  <si>
+    <t>sbce1</t>
+  </si>
+  <si>
+    <t>10.10.48.186</t>
+  </si>
+  <si>
+    <t>lab.local</t>
+  </si>
+  <si>
+    <t>sbce2</t>
+  </si>
+  <si>
+    <t>10.10.48.187</t>
+  </si>
+  <si>
+    <t>SB</t>
   </si>
 </sst>
 </file>
@@ -837,11 +930,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -887,1344 +981,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="303">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="112">
     <dxf>
       <fill>
         <patternFill>
@@ -3339,28 +2096,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80C5153-2081-4742-A378-369888560B47}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.21875" customWidth="1"/>
+    <col min="2" max="2" width="70.21875" customWidth="1"/>
     <col min="3" max="3" width="108.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s">
         <v>104</v>
       </c>
       <c r="C1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -3368,24 +2128,33 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>95</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
@@ -3394,6 +2163,9 @@
       <c r="A6" t="s">
         <v>60</v>
       </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
       <c r="C6" t="s">
         <v>61</v>
       </c>
@@ -3402,6 +2174,9 @@
       <c r="A7" t="s">
         <v>45</v>
       </c>
+      <c r="B7" t="s">
+        <v>110</v>
+      </c>
       <c r="C7" t="s">
         <v>62</v>
       </c>
@@ -3421,6 +2196,9 @@
       <c r="A9" t="s">
         <v>5</v>
       </c>
+      <c r="B9" t="s">
+        <v>130</v>
+      </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
@@ -3430,7 +2208,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -3440,6 +2218,9 @@
       <c r="A11" t="s">
         <v>51</v>
       </c>
+      <c r="B11" t="s">
+        <v>130</v>
+      </c>
       <c r="C11" t="s">
         <v>52</v>
       </c>
@@ -3460,7 +2241,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -3470,6 +2251,9 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -3478,6 +2262,9 @@
       <c r="A15" t="s">
         <v>16</v>
       </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
       <c r="C15" t="s">
         <v>17</v>
       </c>
@@ -3486,6 +2273,9 @@
       <c r="A16" t="s">
         <v>18</v>
       </c>
+      <c r="B16" t="s">
+        <v>115</v>
+      </c>
       <c r="C16" t="s">
         <v>19</v>
       </c>
@@ -3521,6 +2311,9 @@
       <c r="A20" t="s">
         <v>53</v>
       </c>
+      <c r="B20" t="s">
+        <v>133</v>
+      </c>
       <c r="C20" t="s">
         <v>63</v>
       </c>
@@ -3531,7 +2324,7 @@
       </c>
       <c r="B21" t="str">
         <f>_xlfn.CONCAT(B9, ".", B20)</f>
-        <v>.</v>
+        <v>sbcems.lab.local</v>
       </c>
       <c r="C21" t="s">
         <v>64</v>
@@ -3541,6 +2334,9 @@
       <c r="A22" t="s">
         <v>56</v>
       </c>
+      <c r="B22" t="s">
+        <v>116</v>
+      </c>
       <c r="C22" t="s">
         <v>65</v>
       </c>
@@ -3549,6 +2345,9 @@
       <c r="A23" t="s">
         <v>55</v>
       </c>
+      <c r="B23" t="s">
+        <v>117</v>
+      </c>
       <c r="C23" t="s">
         <v>66</v>
       </c>
@@ -3557,6 +2356,9 @@
       <c r="A24" t="s">
         <v>57</v>
       </c>
+      <c r="B24" t="s">
+        <v>117</v>
+      </c>
       <c r="C24" t="s">
         <v>67</v>
       </c>
@@ -3565,6 +2367,9 @@
       <c r="A25" t="s">
         <v>58</v>
       </c>
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
       <c r="C25" t="s">
         <v>68</v>
       </c>
@@ -3573,6 +2378,9 @@
       <c r="A26" t="s">
         <v>59</v>
       </c>
+      <c r="B26" t="s">
+        <v>119</v>
+      </c>
       <c r="C26" t="s">
         <v>69</v>
       </c>
@@ -3581,14 +2389,20 @@
       <c r="A27" t="s">
         <v>26</v>
       </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
+      <c r="B28" t="s">
+        <v>121</v>
+      </c>
       <c r="C28" t="s">
         <v>28</v>
       </c>
@@ -3605,6 +2419,9 @@
       <c r="A30" t="s">
         <v>31</v>
       </c>
+      <c r="B30" t="s">
+        <v>122</v>
+      </c>
       <c r="C30" t="s">
         <v>32</v>
       </c>
@@ -3673,22 +2490,31 @@
       <c r="A37" t="s">
         <v>72</v>
       </c>
+      <c r="B37" t="s">
+        <v>123</v>
+      </c>
       <c r="C37" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>73</v>
       </c>
+      <c r="B38" t="s">
+        <v>124</v>
+      </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>74</v>
       </c>
+      <c r="B39" t="s">
+        <v>123</v>
+      </c>
       <c r="C39" t="s">
         <v>75</v>
       </c>
@@ -3697,6 +2523,9 @@
       <c r="A40" t="s">
         <v>76</v>
       </c>
+      <c r="B40" t="s">
+        <v>123</v>
+      </c>
       <c r="C40" t="s">
         <v>77</v>
       </c>
@@ -3705,6 +2534,9 @@
       <c r="A41" t="s">
         <v>78</v>
       </c>
+      <c r="B41" t="s">
+        <v>125</v>
+      </c>
       <c r="C41" t="s">
         <v>79</v>
       </c>
@@ -3713,6 +2545,9 @@
       <c r="A42" t="s">
         <v>80</v>
       </c>
+      <c r="B42" t="s">
+        <v>125</v>
+      </c>
       <c r="C42" t="s">
         <v>81</v>
       </c>
@@ -3737,6 +2572,9 @@
       <c r="A45" t="s">
         <v>82</v>
       </c>
+      <c r="B45" t="s">
+        <v>74</v>
+      </c>
       <c r="C45" t="s">
         <v>83</v>
       </c>
@@ -3745,6 +2583,9 @@
       <c r="A46" t="s">
         <v>84</v>
       </c>
+      <c r="B46" t="s">
+        <v>127</v>
+      </c>
       <c r="C46" t="s">
         <v>85</v>
       </c>
@@ -3753,6 +2594,9 @@
       <c r="A47" t="s">
         <v>86</v>
       </c>
+      <c r="B47" t="s">
+        <v>112</v>
+      </c>
       <c r="C47" t="s">
         <v>87</v>
       </c>
@@ -3761,40 +2605,1382 @@
       <c r="A48" t="s">
         <v>88</v>
       </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
       <c r="C48" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="B49" t="s">
+        <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="44" priority="23">
+    <cfRule type="expression" dxfId="111" priority="24">
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
+    <cfRule type="expression" dxfId="110" priority="23">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="expression" dxfId="109" priority="21">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="expression" dxfId="108" priority="20">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="expression" dxfId="107" priority="19">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="expression" dxfId="106" priority="18">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="expression" dxfId="105" priority="17">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="expression" dxfId="104" priority="16">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="expression" dxfId="103" priority="15">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="expression" dxfId="102" priority="14">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39">
+    <cfRule type="expression" dxfId="101" priority="13">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40">
+    <cfRule type="expression" dxfId="100" priority="12">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="expression" dxfId="99" priority="11">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="expression" dxfId="98" priority="10">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="expression" dxfId="97" priority="9">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="expression" dxfId="96" priority="8">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45">
+    <cfRule type="expression" dxfId="95" priority="7">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="expression" dxfId="94" priority="6">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47">
+    <cfRule type="expression" dxfId="93" priority="5">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="expression" dxfId="92" priority="4">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="expression" dxfId="91" priority="3">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="expression" dxfId="90" priority="2">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" dxfId="89" priority="1">
+      <formula>B10&lt;&gt;"EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="16">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{392BA8B5-DFCE-4FAD-B98D-8723D09F28FD}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{EBC16548-B245-4CF4-939A-FDA1B969F099}">
+      <formula1>"DUAL_STACK,IPV4"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{8D0C82A1-92F9-4D92-984E-E31181D72A49}">
+      <formula1>21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{5A574EEA-ADF1-4FFB-ACA2-17FCEA8094CD}">
+      <formula1>"ESXI,KVM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10" xr:uid="{80DC45CB-068F-4FBD-B3C8-4ABE944DC6ED}">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{9E9590C0-45C5-4BD8-9C2E-FE8C612E3CFE}">
+      <formula1>"primary,secondary"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{418585B9-E084-4EF8-90E7-B9429671DD54}">
+      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{6617306C-E92F-4A25-8274-DA7845B13381}">
+      <formula1>"A1,A2,B1,B2"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{8F97596A-C92B-4D5D-A04F-2BA11D7593A6}">
+      <formula1>$B$1="ESXI"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12 B31 B32" xr:uid="{8C8535BF-93DC-4848-9137-7B1AA5EE720F}">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21 B22 B23 B24 B25 B26" xr:uid="{2A141C2C-0280-4199-A350-7F8284E8D5E3}">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B39 B40 B41 B42 B46 B47 B48 B49 B50" xr:uid="{2ACC0FDE-CD74-4F6F-A3A3-DAA46DB91C3F}">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B44" xr:uid="{D1FAA816-C04B-4EEA-A967-354B27FB605B}">
+      <formula1>$B$10="SBCE"</formula1>
+    </dataValidation>
+    <dataValidation operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{BE5743C8-CDDC-48BE-9E23-0BFF1F54E08C}"/>
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B34 B33 B35" xr:uid="{E10DCD02-B673-4228-8B85-3573B3EFEE1D}">
+      <formula1>7</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{2486B4FA-546B-45E1-8DA1-543A58FE49D7}">
+      <formula1>8</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C46CA50E-BDE1-4748-AAE3-DB4DB9A1B2A5}">
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="108.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="1">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="str">
+        <f>_xlfn.CONCAT(B9, ".", B20)</f>
+        <v>ems.lab.local</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="expression" dxfId="65" priority="22">
+      <formula>B1="KVM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" dxfId="64" priority="21">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="expression" dxfId="63" priority="20">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="expression" dxfId="62" priority="19">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="expression" dxfId="61" priority="18">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="expression" dxfId="60" priority="17">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="expression" dxfId="59" priority="16">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="expression" dxfId="58" priority="15">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="expression" dxfId="57" priority="14">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="expression" dxfId="56" priority="13">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39">
+    <cfRule type="expression" dxfId="55" priority="12">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40">
+    <cfRule type="expression" dxfId="54" priority="11">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="expression" dxfId="53" priority="10">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="expression" dxfId="52" priority="9">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="expression" dxfId="51" priority="8">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="expression" dxfId="50" priority="7">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45">
+    <cfRule type="expression" dxfId="49" priority="6">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="expression" dxfId="48" priority="5">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47">
+    <cfRule type="expression" dxfId="47" priority="4">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="expression" dxfId="46" priority="3">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="expression" dxfId="45" priority="2">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" dxfId="44" priority="1">
+      <formula>B10&lt;&gt;"EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="16">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{EF62750C-8857-4AB1-B612-1A1542DB1E87}">
+      <formula1>8</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B33:B35" xr:uid="{02BB8F85-788A-481B-B4DD-E8A0F530FD36}">
+      <formula1>7</formula1>
+    </dataValidation>
+    <dataValidation operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{374B840C-DF26-4D6A-A825-198722DA6FA5}"/>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43:B44" xr:uid="{9B947BA8-7CE2-4DBD-B25A-A23069793504}">
+      <formula1>$B$10="SBCE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B39:B42 B46:B49" xr:uid="{BFC9206B-37A0-4988-9F2F-2CC6D164F3FA}">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B26" xr:uid="{2F1B8BCB-0A15-4546-AE1A-441EE4E1C35A}">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12 B31:B32" xr:uid="{E86B3C0C-2413-4E3A-BEF0-07C4C2507BFA}">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{FBA06F15-9014-49EF-BFE5-F66410D319AA}">
+      <formula1>$B$1="ESXI"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{1C138210-67AE-438B-8CBB-8FA5DEEF6A8C}">
+      <formula1>"A1,A2,B1,B2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{DEEFF223-EB8F-4787-A93F-E275895BF6B8}">
+      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{1B876CDA-B7A1-4E84-83F8-86024040D063}">
+      <formula1>"primary,secondary"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10" xr:uid="{3692A704-5E61-4E12-8652-38AEF85F8D3E}">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{73DBF4FE-D6C3-4442-8441-EB71AF75A9F9}">
+      <formula1>"ESXI,KVM"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{BDF3CC34-3406-4C3A-847F-F5CA96D7D372}">
+      <formula1>21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{BC120C32-D2E0-41DC-AC22-9130E9FD16A6}">
+      <formula1>"DUAL_STACK,IPV4"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{DF06827F-5352-4E82-BE83-A8BFE7BA33A9}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C145289A-24B7-4AF1-8664-12CF7BAFE66B}">
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="108.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="1">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" t="s">
+        <v>135</v>
+      </c>
+      <c r="C49" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B5">
     <cfRule type="expression" dxfId="43" priority="22">
+      <formula>B1="KVM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" dxfId="42" priority="21">
       <formula>B10="EMS+SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="expression" dxfId="42" priority="21">
-      <formula>B10&lt;&gt;"EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
@@ -3892,54 +4078,735 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
+  <conditionalFormatting sqref="B13">
     <cfRule type="expression" dxfId="22" priority="1">
+      <formula>B10&lt;&gt;"EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="16">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{67CA13E8-E016-4423-9E76-67C70E6F46AE}">
+      <formula1>8</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B33:B35" xr:uid="{BA7AE130-7A25-43EC-A5DB-0858380A616E}">
+      <formula1>7</formula1>
+    </dataValidation>
+    <dataValidation operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{4B038343-7CCD-49DB-90E3-A4B56CE473DA}"/>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43:B44" xr:uid="{ECC1DC61-D0D9-4E8E-9143-BF230C13BD83}">
+      <formula1>$B$10="SBCE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B39:B42 B46:B49" xr:uid="{6F886349-0D99-4C12-AC53-A4EC1679013F}">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B26" xr:uid="{A8410051-F3D7-4F95-9959-33C5AD99F6DF}">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12 B31:B32" xr:uid="{DAEE9A92-82CC-4FAE-A805-C09BE09E0212}">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{71C081AF-C870-4647-8ADE-1BF83501817D}">
+      <formula1>$B$1="ESXI"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{6CCA4F8F-F58F-4A3A-8580-63A6C06FD65A}">
+      <formula1>"A1,A2,B1,B2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{CAB7A839-1725-4A5D-BDB8-E977BA651B56}">
+      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{FC373F15-8828-49DF-BCDC-883EA220B5EB}">
+      <formula1>"primary,secondary"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10" xr:uid="{941A8A01-355F-4103-89F3-1ECC0E220E27}">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{242A5F8F-1F62-4425-B3AF-DCEC672748D0}">
+      <formula1>"ESXI,KVM"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{6E656042-C4E2-4540-869B-472D1F17D262}">
+      <formula1>21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{67E7179D-7A08-4F94-B4B9-C8D02504E956}">
+      <formula1>"DUAL_STACK,IPV4"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{69C485A8-4924-44BB-A156-918BEEA181F8}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40C88F6-D37C-4D4C-9F6D-B126C60B780E}">
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="108.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="1">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" t="s">
+        <v>135</v>
+      </c>
+      <c r="C49" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="expression" dxfId="21" priority="22">
+      <formula>B1="KVM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" dxfId="20" priority="21">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="expression" dxfId="19" priority="20">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="expression" dxfId="18" priority="19">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{88A269AF-C549-4C18-B2ED-5D861C483F64}">
-      <formula1>"KVM, ESXi"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{392BA8B5-DFCE-4FAD-B98D-8723D09F28FD}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{EBC16548-B245-4CF4-939A-FDA1B969F099}">
+  <conditionalFormatting sqref="B40">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>B10&lt;&gt;"EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="16">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{9CDFC943-7388-48AF-AD1B-3E50DD0CF0E7}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{A8333A30-E8A9-468B-9448-D18959240DFC}">
       <formula1>"DUAL_STACK,IPV4"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{BF1A903F-7866-449A-A507-55139B39DAD6}">
-      <formula1>"DUAL_STACK"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{8D0C82A1-92F9-4D92-984E-E31181D72A49}">
-      <formula1>"none, primary, secondary"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{5A574EEA-ADF1-4FFB-ACA2-17FCEA8094CD}">
+    <dataValidation type="textLength" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{B37D3233-A062-4AE9-83B5-09B95453A148}">
+      <formula1>21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{04F578E3-B65E-4A05-9C01-6E614F59F6F1}">
       <formula1>"ESXI,KVM"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10" xr:uid="{80DC45CB-068F-4FBD-B3C8-4ABE944DC6ED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10" xr:uid="{E2350EE9-2CE2-45BC-A1CC-B32925A0B52C}">
       <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{9E9590C0-45C5-4BD8-9C2E-FE8C612E3CFE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{717F3864-B273-4E2C-B878-EF25CE118B6C}">
       <formula1>"primary,secondary"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{418585B9-E084-4EF8-90E7-B9429671DD54}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{D0FC8359-F84F-456C-95CD-0C9BDD57E80C}">
       <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{6617306C-E92F-4A25-8274-DA7845B13381}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{E028E9F8-6DAB-4545-AAE2-710B220689B9}">
       <formula1>"A1,A2,B1,B2"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{8F97596A-C92B-4D5D-A04F-2BA11D7593A6}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{C05F9D34-6CA2-4244-8651-728D321B5A3E}">
       <formula1>$B$1="ESXI"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12 B31 B32" xr:uid="{8C8535BF-93DC-4848-9137-7B1AA5EE720F}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12 B31:B32" xr:uid="{52D9A5C0-9ECD-4C67-A861-9CCFEAAC2893}">
       <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21 B22 B23 B24 B25 B26" xr:uid="{2A141C2C-0280-4199-A350-7F8284E8D5E3}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B26" xr:uid="{40269542-6DA9-48EE-89AC-695409F51CC2}">
       <formula1>$B$10&lt;&gt;"SBCE"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B39 B40 B41 B42 B46 B47 B48 B49 B50" xr:uid="{2ACC0FDE-CD74-4F6F-A3A3-DAA46DB91C3F}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B39:B42 B46:B49" xr:uid="{6E4033C5-BB85-46FF-9172-6B47A6F2BAC7}">
       <formula1>$B$10&lt;&gt;"EMS"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B44" xr:uid="{D1FAA816-C04B-4EEA-A967-354B27FB605B}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43:B44" xr:uid="{C130AC9E-4423-4C5E-81FB-28986A6D7C68}">
       <formula1>$B$10="SBCE"</formula1>
+    </dataValidation>
+    <dataValidation operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{0DCB0AAB-BEB2-4245-A372-959DF3645554}"/>
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B33:B35" xr:uid="{AE0A8769-56C8-48D5-945C-86F37D4D12AD}">
+      <formula1>7</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{7B3648C2-D253-407A-B777-42CFEFA3BB34}">
+      <formula1>8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/csv/sbce_config.xlsx
+++ b/data/csv/sbce_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszokoly\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFED17C2-9494-41FF-B348-A9909413A92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAC8B52-D57E-4634-B243-640C9474AAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{B9974296-33B4-464A-B6B3-E66B7C96D59B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9974296-33B4-464A-B6B3-E66B7C96D59B}"/>
   </bookViews>
   <sheets>
     <sheet name="SBCEMS" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="148">
   <si>
     <t>datastore</t>
   </si>
@@ -342,9 +342,6 @@
     <t>M1 NIC Port-group / Bridge name</t>
   </si>
   <si>
-    <t>Time Zone - Time Zone in which device is located in GMT</t>
-  </si>
-  <si>
     <t>EMS+SBCE</t>
   </si>
   <si>
@@ -402,9 +399,6 @@
     <t>CA</t>
   </si>
   <si>
-    <t>GMT-7</t>
-  </si>
-  <si>
     <t>10.10.48.250</t>
   </si>
   <si>
@@ -481,6 +475,15 @@
   </si>
   <si>
     <t>10.10.48.200</t>
+  </si>
+  <si>
+    <t>America/Edmonton</t>
+  </si>
+  <si>
+    <t>Time Zone - Time Zone in which device is located (for example America/Edmonton)</t>
+  </si>
+  <si>
+    <t>Time Zone - Time Zone in which device is located  (for example America/Edmonton)</t>
   </si>
 </sst>
 </file>
@@ -2597,7 +2600,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -2608,7 +2611,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -2619,7 +2622,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -2630,7 +2633,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -2641,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -2652,7 +2655,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -2663,7 +2666,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -2685,7 +2688,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -2696,7 +2699,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -2707,7 +2710,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -2740,7 +2743,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -2751,7 +2754,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -2762,7 +2765,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -2800,7 +2803,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -2823,7 +2826,7 @@
         <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
         <v>65</v>
@@ -2834,7 +2837,7 @@
         <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
         <v>66</v>
@@ -2845,7 +2848,7 @@
         <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
         <v>67</v>
@@ -2856,7 +2859,7 @@
         <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -2867,7 +2870,7 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>69</v>
@@ -2878,10 +2881,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -2889,7 +2892,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -2908,7 +2911,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -2979,7 +2982,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -2990,7 +2993,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -3001,7 +3004,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -3012,7 +3015,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -3023,7 +3026,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -3034,7 +3037,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -3072,7 +3075,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -3083,7 +3086,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -3094,10 +3097,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -3105,10 +3108,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3227,7 +3230,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{392BA8B5-DFCE-4FAD-B98D-8723D09F28FD}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{EBC16548-B245-4CF4-939A-FDA1B969F099}">
       <formula1>"DUAL_STACK,IPV4"</formula1>
@@ -3243,9 +3246,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{9E9590C0-45C5-4BD8-9C2E-FE8C612E3CFE}">
       <formula1>"primary,secondary"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{418585B9-E084-4EF8-90E7-B9429671DD54}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{6617306C-E92F-4A25-8274-DA7845B13381}">
       <formula1>"A1,A2,B1,B2"</formula1>
@@ -3293,7 +3293,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -3304,7 +3304,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -3315,7 +3315,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -3326,7 +3326,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -3337,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -3348,7 +3348,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -3359,7 +3359,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -3381,7 +3381,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -3392,7 +3392,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -3403,7 +3403,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -3436,7 +3436,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -3447,7 +3447,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -3458,7 +3458,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -3496,7 +3496,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -3519,7 +3519,7 @@
         <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
         <v>65</v>
@@ -3530,7 +3530,7 @@
         <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
         <v>66</v>
@@ -3541,7 +3541,7 @@
         <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
         <v>67</v>
@@ -3552,7 +3552,7 @@
         <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -3563,7 +3563,7 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>69</v>
@@ -3574,10 +3574,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -3585,7 +3585,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -3604,7 +3604,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -3675,7 +3675,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -3686,7 +3686,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -3769,7 +3769,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -3777,7 +3777,7 @@
         <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3891,7 +3891,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{EF62750C-8857-4AB1-B612-1A1542DB1E87}">
       <formula1>8</formula1>
     </dataValidation>
@@ -3916,9 +3916,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{1C138210-67AE-438B-8CBB-8FA5DEEF6A8C}">
       <formula1>"A1,A2,B1,B2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{DEEFF223-EB8F-4787-A93F-E275895BF6B8}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{1B876CDA-B7A1-4E84-83F8-86024040D063}">
       <formula1>"primary,secondary"</formula1>
@@ -3956,7 +3953,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -3967,7 +3964,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -3978,7 +3975,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -3989,7 +3986,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -4000,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -4011,7 +4008,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -4022,7 +4019,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -4044,7 +4041,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -4055,7 +4052,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -4066,7 +4063,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -4099,7 +4096,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -4110,7 +4107,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -4121,7 +4118,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -4159,7 +4156,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -4218,10 +4215,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -4229,7 +4226,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -4248,7 +4245,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -4259,7 +4256,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -4322,7 +4319,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -4333,7 +4330,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -4344,7 +4341,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -4355,7 +4352,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -4366,7 +4363,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -4377,7 +4374,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -4388,7 +4385,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
         <v>48</v>
@@ -4399,7 +4396,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
@@ -4421,7 +4418,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -4432,7 +4429,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -4443,10 +4440,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -4454,10 +4451,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4571,7 +4568,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{67CA13E8-E016-4423-9E76-67C70E6F46AE}">
       <formula1>8</formula1>
     </dataValidation>
@@ -4596,9 +4593,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{6CCA4F8F-F58F-4A3A-8580-63A6C06FD65A}">
       <formula1>"A1,A2,B1,B2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{CAB7A839-1725-4A5D-BDB8-E977BA651B56}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{FC373F15-8828-49DF-BCDC-883EA220B5EB}">
       <formula1>"primary,secondary"</formula1>
@@ -4636,7 +4630,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -4647,7 +4641,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -4658,7 +4652,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -4669,7 +4663,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -4680,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -4691,7 +4685,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -4702,7 +4696,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -4724,7 +4718,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -4735,7 +4729,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -4746,7 +4740,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -4779,7 +4773,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -4790,7 +4784,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -4801,7 +4795,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -4839,7 +4833,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -4898,10 +4892,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -4909,7 +4903,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -4928,7 +4922,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -4939,7 +4933,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -5002,7 +4996,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -5013,7 +5007,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -5024,7 +5018,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -5035,7 +5029,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -5046,7 +5040,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -5057,7 +5051,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -5068,7 +5062,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C43" t="s">
         <v>48</v>
@@ -5079,7 +5073,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
@@ -5101,7 +5095,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -5112,7 +5106,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -5123,10 +5117,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -5134,10 +5128,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -5251,7 +5245,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{9CDFC943-7388-48AF-AD1B-3E50DD0CF0E7}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{A8333A30-E8A9-468B-9448-D18959240DFC}">
       <formula1>"DUAL_STACK,IPV4"</formula1>
@@ -5267,9 +5261,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{717F3864-B273-4E2C-B878-EF25CE118B6C}">
       <formula1>"primary,secondary"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{D0FC8359-F84F-456C-95CD-0C9BDD57E80C}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{E028E9F8-6DAB-4545-AAE2-710B220689B9}">
       <formula1>"A1,A2,B1,B2"</formula1>
@@ -5316,7 +5307,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -5327,7 +5318,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -5338,7 +5329,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -5349,7 +5340,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -5360,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -5371,7 +5362,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -5382,7 +5373,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -5404,7 +5395,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -5415,7 +5406,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -5426,7 +5417,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -5459,7 +5450,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -5470,7 +5461,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -5481,7 +5472,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -5519,7 +5510,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -5542,7 +5533,7 @@
         <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
         <v>65</v>
@@ -5553,7 +5544,7 @@
         <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
         <v>66</v>
@@ -5564,7 +5555,7 @@
         <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
         <v>67</v>
@@ -5575,7 +5566,7 @@
         <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -5586,7 +5577,7 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>69</v>
@@ -5597,10 +5588,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -5608,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -5627,7 +5618,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -5698,7 +5689,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -5709,7 +5700,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -5792,7 +5783,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -5800,7 +5791,7 @@
         <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -5914,7 +5905,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{203A9BDA-7863-4615-A22B-52374A439B24}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{2F8FB1CB-92F7-4ADC-A186-44E9FD59E1A4}">
       <formula1>"DUAL_STACK,IPV4"</formula1>
@@ -5930,9 +5921,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{E0F141F2-4E1E-4356-8BA4-D6D05AA21F65}">
       <formula1>"primary,secondary"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{4BA2C49C-DF44-469B-AAFB-EE6BA426F76C}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{66805C94-14D3-445E-B9F4-354B83DE5AB6}">
       <formula1>"A1,A2,B1,B2"</formula1>
@@ -5979,7 +5967,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -5990,7 +5978,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -6001,7 +5989,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -6012,7 +6000,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -6023,7 +6011,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -6034,7 +6022,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -6045,7 +6033,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -6067,7 +6055,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -6078,7 +6066,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -6089,7 +6077,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -6122,7 +6110,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -6133,7 +6121,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -6144,7 +6132,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -6182,7 +6170,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -6241,10 +6229,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -6252,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -6271,7 +6259,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -6282,7 +6270,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -6345,7 +6333,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -6356,7 +6344,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -6367,7 +6355,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -6378,7 +6366,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -6389,7 +6377,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -6400,7 +6388,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -6411,7 +6399,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C43" t="s">
         <v>48</v>
@@ -6422,7 +6410,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
@@ -6444,7 +6432,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -6455,7 +6443,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -6466,10 +6454,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -6477,10 +6465,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -6594,7 +6582,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{FA3A7B80-07D9-4825-A615-8BD925E9A05B}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{D8E0870F-3232-41F6-B6A1-0FEFB6F32BEC}">
       <formula1>"DUAL_STACK,IPV4"</formula1>
@@ -6610,9 +6598,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{6C6982DB-D9DE-4130-91B5-F3C69078F64E}">
       <formula1>"primary,secondary"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{4D7A7E39-B4CD-4684-BF9C-E747FC364C9C}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{7A665DB2-9C16-4CF0-8005-36158EA79B67}">
       <formula1>"A1,A2,B1,B2"</formula1>
@@ -6659,7 +6644,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -6670,7 +6655,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -6681,7 +6666,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -6692,7 +6677,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -6703,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -6714,7 +6699,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -6725,7 +6710,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -6747,7 +6732,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -6758,7 +6743,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -6769,7 +6754,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -6802,7 +6787,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -6813,7 +6798,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -6824,7 +6809,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -6862,7 +6847,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -6921,10 +6906,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -6932,7 +6917,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -6951,7 +6936,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -6962,7 +6947,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -7025,7 +7010,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -7036,7 +7021,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -7047,7 +7032,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -7058,7 +7043,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -7069,7 +7054,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -7080,7 +7065,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -7091,7 +7076,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
         <v>48</v>
@@ -7102,7 +7087,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
@@ -7124,7 +7109,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -7135,7 +7120,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -7146,10 +7131,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -7157,10 +7142,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -7274,7 +7259,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{5A5820D3-99F5-447E-9698-788C3515B4E8}">
       <formula1>8</formula1>
     </dataValidation>
@@ -7299,9 +7284,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{0A380C42-ECEE-49B9-8CD7-617B0442832E}">
       <formula1>"A1,A2,B1,B2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{85EF6794-38BD-4967-9600-2C767C5DE227}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{31802C4A-0599-49EF-A550-CFE48CD453EE}">
       <formula1>"primary,secondary"</formula1>
@@ -7339,7 +7321,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -7350,7 +7332,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -7361,7 +7343,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -7372,7 +7354,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -7383,7 +7365,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -7394,7 +7376,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -7405,7 +7387,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -7427,7 +7409,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -7438,7 +7420,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -7449,7 +7431,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -7482,7 +7464,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -7493,7 +7475,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -7504,7 +7486,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -7542,7 +7524,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -7601,10 +7583,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -7612,7 +7594,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -7631,7 +7613,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -7642,7 +7624,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -7705,7 +7687,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -7716,7 +7698,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -7727,7 +7709,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -7738,7 +7720,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -7749,7 +7731,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -7760,7 +7742,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -7798,7 +7780,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -7809,7 +7791,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -7820,10 +7802,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -7831,10 +7813,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -7948,7 +7930,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{67DFEABE-E9D9-492A-B08E-BC5D4A7DB198}">
       <formula1>8</formula1>
     </dataValidation>
@@ -7973,9 +7955,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{08AF66F3-57CB-4199-ABA0-AA25F929E71A}">
       <formula1>"A1,A2,B1,B2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{08488717-1CD6-44C5-946D-7721D9E5AE65}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{D264AB75-6254-4A82-82FB-610BF04E4231}">
       <formula1>"primary,secondary"</formula1>
